--- a/artfynd/A 36599-2023 artfynd.xlsx
+++ b/artfynd/A 36599-2023 artfynd.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 36599-2023 artfynd.xlsx
+++ b/artfynd/A 36599-2023 artfynd.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 36599-2023 artfynd.xlsx
+++ b/artfynd/A 36599-2023 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Falk, Alexander Singer</t>
+          <t>Alexander Singer, Håkan Falk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 36599-2023 artfynd.xlsx
+++ b/artfynd/A 36599-2023 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexander Singer, Håkan Falk</t>
+          <t>Håkan Falk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 36599-2023 artfynd.xlsx
+++ b/artfynd/A 36599-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668999</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668848</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668993</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668894</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669017</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669004</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669006</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669007</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669008</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669011</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668828</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668968</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668974</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668976</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668978</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668979</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668981</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668982</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668990</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668992</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669018</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669019</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668824</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668931</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668932</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668934</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668935</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668833</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668836</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668870</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668924</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669013</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669015</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669016</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668996</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668936</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668944</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668952</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668957</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668881</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668910</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668838</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668840</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,8 +5568,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134668868</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>